--- a/sample_upload.xlsx
+++ b/sample_upload.xlsx
@@ -439,28 +439,28 @@
         <v>Ahmed Al Mansouri</v>
       </c>
       <c r="B2" t="str">
-        <v>971501234567</v>
+        <v>971501234501</v>
       </c>
       <c r="C2" t="str">
-        <v>971551234567</v>
+        <v>971501234502</v>
       </c>
       <c r="D2" t="str">
         <v>ahmed@example.com</v>
       </c>
       <c r="E2" t="str">
-        <v>Marina Tower A</v>
+        <v>Burj Crown</v>
       </c>
       <c r="F2" t="str">
-        <v>1204</v>
+        <v>1201</v>
       </c>
       <c r="G2" t="str">
-        <v>Dubai Marina</v>
+        <v>Downtown Dubai</v>
       </c>
       <c r="H2" t="str">
-        <v>P-17742699876171</v>
+        <v>P-TEST-001</v>
       </c>
       <c r="I2" t="str">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="J2" t="str">
         <v>2BR</v>
@@ -474,7 +474,7 @@
         <v>Sara Al Hashimi</v>
       </c>
       <c r="B3" t="str">
-        <v>971507654321</v>
+        <v>971502234501</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -483,22 +483,22 @@
         <v>sara@example.com</v>
       </c>
       <c r="E3" t="str">
-        <v>Palm Residences</v>
+        <v>Bellevue Towers</v>
       </c>
       <c r="F3" t="str">
-        <v>305</v>
+        <v>805</v>
       </c>
       <c r="G3" t="str">
-        <v>Palm Jumeirah</v>
+        <v>Business Bay</v>
       </c>
       <c r="H3" t="str">
-        <v>P-17742699876172</v>
+        <v>P-TEST-002</v>
       </c>
       <c r="I3" t="str">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="J3" t="str">
-        <v>3BR</v>
+        <v>1BR</v>
       </c>
       <c r="K3" t="str">
         <v>Owner</v>
@@ -506,37 +506,37 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Mohammed Al Rashid</v>
+        <v>Mohammed Al Farsi</v>
       </c>
       <c r="B4" t="str">
-        <v>971509876543</v>
+        <v>971503234501</v>
       </c>
       <c r="C4" t="str">
-        <v>971559876543</v>
+        <v/>
       </c>
       <c r="D4" t="str">
         <v/>
       </c>
       <c r="E4" t="str">
-        <v>Downtown Heights</v>
+        <v>Downtown Views</v>
       </c>
       <c r="F4" t="str">
-        <v>802</v>
+        <v>304</v>
       </c>
       <c r="G4" t="str">
         <v>Downtown Dubai</v>
       </c>
       <c r="H4" t="str">
-        <v>P-17742699876173</v>
+        <v>P-TEST-003</v>
       </c>
       <c r="I4" t="str">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="J4" t="str">
-        <v>1BR</v>
+        <v>3BR</v>
       </c>
       <c r="K4" t="str">
-        <v>Owner</v>
+        <v>Lead</v>
       </c>
     </row>
     <row r="5">
@@ -544,31 +544,31 @@
         <v>Fatima Al Zaabi</v>
       </c>
       <c r="B5" t="str">
-        <v>971503456789</v>
+        <v>971504234501</v>
       </c>
       <c r="C5" t="str">
-        <v/>
+        <v>971504234502</v>
       </c>
       <c r="D5" t="str">
         <v>fatima@example.com</v>
       </c>
       <c r="E5" t="str">
-        <v>JBR Walk Tower</v>
+        <v>Celestia</v>
       </c>
       <c r="F5" t="str">
-        <v>1501</v>
+        <v>112</v>
       </c>
       <c r="G5" t="str">
-        <v>Jumeirah Beach Residence</v>
+        <v>Dubai South</v>
       </c>
       <c r="H5" t="str">
-        <v>P-17742699876174</v>
+        <v>P-TEST-004</v>
       </c>
       <c r="I5" t="str">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="J5" t="str">
-        <v>2BR</v>
+        <v>Studio</v>
       </c>
       <c r="K5" t="str">
         <v>Lead</v>
@@ -579,31 +579,31 @@
         <v>Khalid Al Nuaimi</v>
       </c>
       <c r="B6" t="str">
-        <v>971506543210</v>
+        <v>971505234501</v>
       </c>
       <c r="C6" t="str">
-        <v>971556543210</v>
+        <v/>
       </c>
       <c r="D6" t="str">
         <v>khalid@example.com</v>
       </c>
       <c r="E6" t="str">
-        <v>Business Bay Tower</v>
+        <v>Tenora</v>
       </c>
       <c r="F6" t="str">
         <v>2201</v>
       </c>
       <c r="G6" t="str">
-        <v>Business Bay</v>
+        <v>Dubai South</v>
       </c>
       <c r="H6" t="str">
-        <v>P-17742699876175</v>
+        <v>P-TEST-005</v>
       </c>
       <c r="I6" t="str">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="J6" t="str">
-        <v>Studio</v>
+        <v>2BR</v>
       </c>
       <c r="K6" t="str">
         <v>Owner</v>
